--- a/配合期货.xlsx
+++ b/配合期货.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minghaochen/Desktop/Futures_Derivative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5776387-B4B1-924F-A4F6-A2DE66CA5C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C418AA-F782-E24F-9FD3-FAAF8FC17F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="960" windowWidth="26940" windowHeight="14860" activeTab="1" xr2:uid="{01478177-066F-684A-96FD-4867F9812F85}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" activeTab="1" xr2:uid="{01478177-066F-684A-96FD-4867F9812F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="加权平均" sheetId="3" r:id="rId2"/>
+    <sheet name="FIRO" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -176,23 +176,32 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>plus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>price</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加权价</t>
+    <t>1手 @ 7590.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1手 @ 7591.50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S
+E
+L
+L
+6
+手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        剩余的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -200,10 +209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.000000"/>
-  </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -238,8 +244,21 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="MicrosoftYaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="MicrosoftYaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,8 +271,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -270,13 +307,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -301,17 +418,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -328,6 +481,64 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>65368</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>196102</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>336176</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>74706</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直线箭头连接符 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6E519BA-9EF4-AE90-CBD1-03D3C9F9BF87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3090956" y="1783602"/>
+          <a:ext cx="578970" cy="569633"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1112,160 +1323,97 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A97F4E-4FC7-2747-84E4-D1B000C65F3D}">
-  <dimension ref="A1:C18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3AF63AB-92B8-FF4B-B853-6F3A189B901B}">
+  <dimension ref="A5:K14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" style="8" customWidth="1"/>
+    <col min="3" max="4" width="3.140625" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="5" spans="1:11" ht="19" thickBot="1"/>
+    <row r="6" spans="1:11">
+      <c r="B6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="17"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" spans="1:11" ht="19" thickBot="1">
+      <c r="B10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="F10" s="23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19" thickBot="1">
+      <c r="B11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="20"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="F12" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19" thickBot="1">
+      <c r="A13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B13" s="14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="9">
-        <v>7591.25</v>
-      </c>
-      <c r="B2" s="9">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <f>A2*B2</f>
-        <v>7591.25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="9">
-        <v>7592.75</v>
-      </c>
-      <c r="B3" s="9">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:C16" si="0">A3*B3</f>
-        <v>15185.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="10">
-        <v>7608.5</v>
-      </c>
-      <c r="B4" s="9">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8">
-        <f t="shared" si="0"/>
-        <v>7608.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="C15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B17">
-        <f>SUM(B2:B16)</f>
-        <v>4</v>
-      </c>
-      <c r="C17">
-        <f>SUM(C2:C16)</f>
-        <v>30385.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="11">
-        <f>C17/B17</f>
-        <v>7596.3125</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D8:D13"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>